--- a/data/trans_orig/P44-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P44-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012 (tasa de respuesta: 97,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>11684</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>31256</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22732</t>
+          <t>23809</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46379</t>
+          <t>46162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106967</t>
+          <t>108570</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126878</t>
+          <t>128142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36008</t>
+          <t>35990</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49793</t>
+          <t>50080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150869</t>
+          <t>151086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174516</t>
+          <t>173439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25566</t>
+          <t>24920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15571</t>
+          <t>16321</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36814</t>
+          <t>35943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121083</t>
+          <t>121729</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137110</t>
+          <t>137392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>52043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63969</t>
+          <t>64601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177736</t>
+          <t>178607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198979</t>
+          <t>198229</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,39%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18965</t>
+          <t>18518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43577</t>
+          <t>42611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>28057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55154</t>
+          <t>54989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212805</t>
+          <t>213771</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237417</t>
+          <t>237864</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97709</t>
+          <t>98435</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112767</t>
+          <t>113161</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319528</t>
+          <t>319693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346782</t>
+          <t>346625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26955</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53834</t>
+          <t>52559</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9032</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24824</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41235</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71737</t>
+          <t>72225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>403376</t>
+          <t>404651</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430255</t>
+          <t>429649</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>171445</t>
+          <t>172479</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187140</t>
+          <t>187237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>581743</t>
+          <t>581255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>612245</t>
+          <t>612336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16692</t>
+          <t>18038</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>17960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>38593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25643</t>
+          <t>25589</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49191</t>
+          <t>51153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>173253</t>
+          <t>171907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185714</t>
+          <t>185598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>319051</t>
+          <t>320452</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>341374</t>
+          <t>341085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>499798</t>
+          <t>497836</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>523346</t>
+          <t>523400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24569</t>
+          <t>24629</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47381</t>
+          <t>48511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23118</t>
+          <t>23847</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47548</t>
+          <t>46814</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2573</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>615989</t>
+          <t>614859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>638801</t>
+          <t>638741</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>619858</t>
+          <t>620592</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>644288</t>
+          <t>643559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92764</t>
+          <t>91941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138282</t>
+          <t>138120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90348</t>
+          <t>89432</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132333</t>
+          <t>129108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>193009</t>
+          <t>190883</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>257516</t>
+          <t>253852</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1055767</t>
+          <t>1055929</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1101285</t>
+          <t>1102108</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1329973</t>
+          <t>1333198</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1371958</t>
+          <t>1372874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2398838</t>
+          <t>2402502</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2463345</t>
+          <t>2465471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21238</t>
+          <t>21097</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43835</t>
+          <t>42494</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19333</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29957</t>
+          <t>29861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>56059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129201</t>
+          <t>130542</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151798</t>
+          <t>151939</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90040</t>
+          <t>89559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104406</t>
+          <t>104388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>224806</t>
+          <t>226350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252452</t>
+          <t>252548</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,43%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>37298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>22585</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44932</t>
+          <t>45876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105566</t>
+          <t>106155</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125214</t>
+          <t>124626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84639</t>
+          <t>84044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93998</t>
+          <t>94014</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194636</t>
+          <t>193692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217295</t>
+          <t>216983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20571</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41731</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3132</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13973</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>27376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51267</t>
+          <t>51618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225979</t>
+          <t>225639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>247139</t>
+          <t>247200</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67471</t>
+          <t>66717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78312</t>
+          <t>78252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297886</t>
+          <t>297535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323216</t>
+          <t>321777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40253</t>
+          <t>39569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68495</t>
+          <t>66227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14979</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36297</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61295</t>
+          <t>60941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95811</t>
+          <t>94016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>466058</t>
+          <t>468326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>494300</t>
+          <t>494984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219644</t>
+          <t>219439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240962</t>
+          <t>240463</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>694683</t>
+          <t>696478</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>729199</t>
+          <t>729553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35133</t>
+          <t>35231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>42748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40492</t>
+          <t>41851</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69130</t>
+          <t>71098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>237681</t>
+          <t>237583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255597</t>
+          <t>255375</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>339230</t>
+          <t>338544</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>361647</t>
+          <t>361110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>584975</t>
+          <t>583007</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>613613</t>
+          <t>612254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28511</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>53421</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28767</t>
+          <t>28706</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54430</t>
+          <t>55062</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>605606</t>
+          <t>608175</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>633085</t>
+          <t>634148</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>612870</t>
+          <t>612238</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>638533</t>
+          <t>638594</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>141757</t>
+          <t>142753</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>189267</t>
+          <t>190301</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95309</t>
+          <t>97571</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>140067</t>
+          <t>141337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252502</t>
+          <t>249531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>316205</t>
+          <t>318911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1208002</t>
+          <t>1206968</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1255512</t>
+          <t>1254516</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1445694</t>
+          <t>1444424</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1490452</t>
+          <t>1488190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2666825</t>
+          <t>2664119</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2730528</t>
+          <t>2733499</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,63%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023 (tasa de respuesta: 98,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116996</t>
+          <t>113547</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>144694</t>
+          <t>142165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63221</t>
+          <t>63894</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83579</t>
+          <t>83324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185217</t>
+          <t>185344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220051</t>
+          <t>218889</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106603</t>
+          <t>109132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134301</t>
+          <t>137750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91554</t>
+          <t>91809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111912</t>
+          <t>111239</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206380</t>
+          <t>207542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241214</t>
+          <t>241087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70661</t>
+          <t>69855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96326</t>
+          <t>96153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41261</t>
+          <t>41713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57976</t>
+          <t>58206</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117793</t>
+          <t>116245</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147934</t>
+          <t>146607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123775</t>
+          <t>123948</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149440</t>
+          <t>150246</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82701</t>
+          <t>82471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99416</t>
+          <t>98964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212844</t>
+          <t>214171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242985</t>
+          <t>244533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173714</t>
+          <t>175766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>418336</t>
+          <t>421855</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39961</t>
+          <t>39195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201745</t>
+          <t>200799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>495430</t>
+          <t>487200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>38021</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>286162</t>
+          <t>284110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60111</t>
+          <t>60877</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74237</t>
+          <t>74261</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64519</t>
+          <t>72749</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358204</t>
+          <t>359150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,14%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142462</t>
+          <t>141685</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180898</t>
+          <t>180430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>151840</t>
+          <t>149136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124828</t>
+          <t>124408</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>318120</t>
+          <t>317244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326793</t>
+          <t>327261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>365229</t>
+          <t>366006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348176</t>
+          <t>350880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470894</t>
+          <t>470332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>689587</t>
+          <t>690463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>882879</t>
+          <t>883299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56506</t>
+          <t>55306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81148</t>
+          <t>79419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98516</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124747</t>
+          <t>124710</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>159945</t>
+          <t>160583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196721</t>
+          <t>195935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,8%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152406</t>
+          <t>154135</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177048</t>
+          <t>178248</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>299302</t>
+          <t>299339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>325533</t>
+          <t>326015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>460882</t>
+          <t>461668</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>497658</t>
+          <t>497020</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1576</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107024</t>
+          <t>107219</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>134327</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111479</t>
+          <t>111248</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>138560</t>
+          <t>139862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>307508</t>
+          <t>306600</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>333903</t>
+          <t>333708</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>313824</t>
+          <t>312522</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>340905</t>
+          <t>341136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,41%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>603748</t>
+          <t>604527</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1132541</t>
+          <t>1099495</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>292847</t>
+          <t>324640</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>545367</t>
+          <t>543936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1031074</t>
+          <t>1037566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1766515</t>
+          <t>1800881</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>551434</t>
+          <t>584480</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1080227</t>
+          <t>1079448</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1235509</t>
+          <t>1236940</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1488029</t>
+          <t>1456236</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1698336</t>
+          <t>1663970</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2433777</t>
+          <t>2427285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P44-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P44-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>11690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23809</t>
+          <t>22165</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46162</t>
+          <t>46874</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108570</t>
+          <t>107944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>128142</t>
+          <t>128136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35990</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50080</t>
+          <t>50130</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151086</t>
+          <t>150374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173439</t>
+          <t>175083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24920</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35943</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121729</t>
+          <t>120756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137392</t>
+          <t>137125</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52043</t>
+          <t>52894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>178607</t>
+          <t>178207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198229</t>
+          <t>198523</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18518</t>
+          <t>19221</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42611</t>
+          <t>43091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>19925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>27820</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54989</t>
+          <t>55077</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,7%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213771</t>
+          <t>213291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237864</t>
+          <t>237161</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98435</t>
+          <t>98375</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113161</t>
+          <t>112633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>319693</t>
+          <t>319605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346625</t>
+          <t>346862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52559</t>
+          <t>52563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9032</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72225</t>
+          <t>69555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>404651</t>
+          <t>404647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>429649</t>
+          <t>430003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172479</t>
+          <t>171868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187237</t>
+          <t>186934</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>581255</t>
+          <t>583925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>612336</t>
+          <t>613546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18038</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38593</t>
+          <t>37544</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25589</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51153</t>
+          <t>50257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>171907</t>
+          <t>172772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185598</t>
+          <t>184793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>320452</t>
+          <t>321501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>341085</t>
+          <t>341544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>497836</t>
+          <t>498732</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>523400</t>
+          <t>522723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48511</t>
+          <t>46229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23847</t>
+          <t>23474</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>47050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>614859</t>
+          <t>617141</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>638741</t>
+          <t>639372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>620592</t>
+          <t>620356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>643559</t>
+          <t>643932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91941</t>
+          <t>92930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>138120</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89432</t>
+          <t>89461</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>129108</t>
+          <t>131536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>190883</t>
+          <t>190928</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>253852</t>
+          <t>254240</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1055929</t>
+          <t>1057096</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1102108</t>
+          <t>1101119</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1333198</t>
+          <t>1330770</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1372874</t>
+          <t>1372845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2402502</t>
+          <t>2402114</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2465471</t>
+          <t>2465426</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21097</t>
+          <t>20938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42494</t>
+          <t>43612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>19820</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29861</t>
+          <t>30023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56059</t>
+          <t>55951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130542</t>
+          <t>129424</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151939</t>
+          <t>152098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89559</t>
+          <t>89553</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>104388</t>
+          <t>104178</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>226350</t>
+          <t>226458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252548</t>
+          <t>252386</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37298</t>
+          <t>38200</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12071</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22585</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45876</t>
+          <t>44181</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>106155</t>
+          <t>105253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124626</t>
+          <t>125239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>84356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>94014</t>
+          <t>94066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193692</t>
+          <t>195387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>216983</t>
+          <t>217126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42071</t>
+          <t>43005</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>27011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51618</t>
+          <t>50131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225639</t>
+          <t>224705</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>247200</t>
+          <t>247141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66717</t>
+          <t>67644</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78252</t>
+          <t>78288</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297535</t>
+          <t>299022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321777</t>
+          <t>322142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39569</t>
+          <t>39487</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66227</t>
+          <t>67113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36502</t>
+          <t>36011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60941</t>
+          <t>61168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94016</t>
+          <t>94878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>468326</t>
+          <t>467440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>494984</t>
+          <t>495066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219439</t>
+          <t>219930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>240463</t>
+          <t>240411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696478</t>
+          <t>695616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>729553</t>
+          <t>729326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>16697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35231</t>
+          <t>34427</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,82 +4754,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>29557</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19305</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>42282</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>11,09%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>54491</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>41767</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>69886</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>6,39%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>29557</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>20182</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42748</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>54491</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>41851</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>71098</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>6,4%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>237583</t>
+          <t>238387</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>255375</t>
+          <t>256117</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,82 +4867,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>93,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>351735</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>339010</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>361987</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>92,25%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>88,91%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>599614</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>584219</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>612338</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>89,32%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>93,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>351735</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>338544</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>361110</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,25%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>88,79%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>599614</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>583007</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>612254</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>91,67%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>89,13%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27448</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53421</t>
+          <t>54946</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28706</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55062</t>
+          <t>54406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>608175</t>
+          <t>606650</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>634148</t>
+          <t>632227</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>612238</t>
+          <t>612894</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>638594</t>
+          <t>639049</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>142753</t>
+          <t>141500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190301</t>
+          <t>191255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97571</t>
+          <t>97055</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141337</t>
+          <t>143204</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>249531</t>
+          <t>252196</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>318911</t>
+          <t>318135</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1206968</t>
+          <t>1206014</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1254516</t>
+          <t>1255769</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1444424</t>
+          <t>1442557</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1488190</t>
+          <t>1488706</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2664119</t>
+          <t>2664895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2733499</t>
+          <t>2730834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -5997,32 +5997,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>129190</t>
+          <t>137732</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113547</t>
+          <t>121935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142165</t>
+          <t>152124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6032,32 +6032,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>73662</t>
+          <t>83088</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63894</t>
+          <t>72789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83324</t>
+          <t>94181</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>202853</t>
+          <t>220820</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185344</t>
+          <t>203128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218889</t>
+          <t>240342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6110,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>122107</t>
+          <t>133557</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109132</t>
+          <t>119165</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137750</t>
+          <t>149354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6145,32 +6145,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>101471</t>
+          <t>111489</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91809</t>
+          <t>100396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111239</t>
+          <t>121788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>223578</t>
+          <t>245046</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>207542</t>
+          <t>225524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241087</t>
+          <t>262738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>251297</t>
+          <t>271289</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>251297</t>
+          <t>271289</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>251297</t>
+          <t>271289</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>175133</t>
+          <t>194577</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>175133</t>
+          <t>194577</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175133</t>
+          <t>194577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>426431</t>
+          <t>465866</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>426431</t>
+          <t>465866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>426431</t>
+          <t>465866</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82796</t>
+          <t>85974</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69855</t>
+          <t>73507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96153</t>
+          <t>100681</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49547</t>
+          <t>55523</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41713</t>
+          <t>46030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58206</t>
+          <t>64530</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>132342</t>
+          <t>141497</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116245</t>
+          <t>124153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146607</t>
+          <t>158682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>137305</t>
+          <t>151669</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123948</t>
+          <t>136962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150246</t>
+          <t>164136</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>91130</t>
+          <t>104040</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82471</t>
+          <t>95033</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98964</t>
+          <t>113533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>228436</t>
+          <t>255709</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214171</t>
+          <t>238524</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244533</t>
+          <t>273053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,74%</t>
         </is>
       </c>
     </row>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>220101</t>
+          <t>237643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>220101</t>
+          <t>237643</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>220101</t>
+          <t>237643</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>140677</t>
+          <t>159563</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140677</t>
+          <t>159563</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>140677</t>
+          <t>159563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>360778</t>
+          <t>397206</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>360778</t>
+          <t>397206</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>360778</t>
+          <t>397206</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6683,32 +6683,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>330058</t>
+          <t>91438</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>175766</t>
+          <t>77849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>421855</t>
+          <t>104932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6718,32 +6718,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32589</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39195</t>
+          <t>43691</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>362648</t>
+          <t>127458</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>200799</t>
+          <t>112566</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>487200</t>
+          <t>144675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>41,66%</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6796,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>129818</t>
+          <t>145892</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38021</t>
+          <t>132398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284110</t>
+          <t>159481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6831,32 +6831,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67483</t>
+          <t>73906</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60877</t>
+          <t>66235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74261</t>
+          <t>81618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>197301</t>
+          <t>219797</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72749</t>
+          <t>202580</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359150</t>
+          <t>234689</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>67,58%</t>
         </is>
       </c>
     </row>
@@ -6909,17 +6909,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>459876</t>
+          <t>237330</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>459876</t>
+          <t>237330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>459876</t>
+          <t>237330</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6944,17 +6944,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100072</t>
+          <t>109926</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100072</t>
+          <t>109926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>100072</t>
+          <t>109926</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>559949</t>
+          <t>347255</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>559949</t>
+          <t>347255</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>559949</t>
+          <t>347255</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7026,32 +7026,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160943</t>
+          <t>175722</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141685</t>
+          <t>157319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180430</t>
+          <t>197239</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7061,32 +7061,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85493</t>
+          <t>93522</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>82586</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149136</t>
+          <t>106839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>246436</t>
+          <t>269243</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124408</t>
+          <t>243598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>317244</t>
+          <t>291209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -7139,32 +7139,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>346748</t>
+          <t>371848</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>327261</t>
+          <t>350331</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>366006</t>
+          <t>390251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7174,32 +7174,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>414523</t>
+          <t>231403</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>350880</t>
+          <t>218086</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470332</t>
+          <t>242339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>761271</t>
+          <t>603252</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>690463</t>
+          <t>581286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>883299</t>
+          <t>628897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>72,08%</t>
         </is>
       </c>
     </row>
@@ -7252,17 +7252,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>507691</t>
+          <t>547570</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>507691</t>
+          <t>547570</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>507691</t>
+          <t>547570</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7287,17 +7287,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>500016</t>
+          <t>324925</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>500016</t>
+          <t>324925</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>500016</t>
+          <t>324925</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1007707</t>
+          <t>872495</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1007707</t>
+          <t>872495</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1007707</t>
+          <t>872495</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7369,32 +7369,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>67607</t>
+          <t>74345</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55306</t>
+          <t>60489</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79419</t>
+          <t>88616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7404,32 +7404,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>110987</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98034</t>
+          <t>106635</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124710</t>
+          <t>133812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>178594</t>
+          <t>194965</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160583</t>
+          <t>176031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>195935</t>
+          <t>215126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -7482,32 +7482,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>165947</t>
+          <t>184731</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>154135</t>
+          <t>170460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178248</t>
+          <t>198587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7517,32 +7517,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>313062</t>
+          <t>336362</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>299339</t>
+          <t>323170</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>326015</t>
+          <t>350347</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>479009</t>
+          <t>521093</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>461668</t>
+          <t>500932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>497020</t>
+          <t>540027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,42%</t>
         </is>
       </c>
     </row>
@@ -7595,17 +7595,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>233554</t>
+          <t>259076</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233554</t>
+          <t>259076</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>233554</t>
+          <t>259076</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>424049</t>
+          <t>456982</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>424049</t>
+          <t>456982</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>424049</t>
+          <t>456982</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>657603</t>
+          <t>716058</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>657603</t>
+          <t>716058</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>657603</t>
+          <t>716058</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7712,32 +7712,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1507</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7747,32 +7747,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>120382</t>
+          <t>132881</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>107219</t>
+          <t>119287</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>134327</t>
+          <t>150105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>124268</t>
+          <t>136730</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111248</t>
+          <t>121198</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>139862</t>
+          <t>151688</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>320545</t>
+          <t>340877</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>306600</t>
+          <t>323653</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>333708</t>
+          <t>354471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>328116</t>
+          <t>348485</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>312522</t>
+          <t>333527</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>341136</t>
+          <t>364017</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,02%</t>
         </is>
       </c>
     </row>
@@ -7973,17 +7973,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>440927</t>
+          <t>473758</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>440927</t>
+          <t>473758</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>440927</t>
+          <t>473758</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>452384</t>
+          <t>485215</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>452384</t>
+          <t>485215</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>452384</t>
+          <t>485215</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8055,32 +8055,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>774479</t>
+          <t>569060</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>604527</t>
+          <t>530548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1099495</t>
+          <t>604812</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8090,32 +8090,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>472662</t>
+          <t>521654</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>324640</t>
+          <t>494548</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>543936</t>
+          <t>550891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1247141</t>
+          <t>1090714</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1037566</t>
+          <t>1045119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1800881</t>
+          <t>1134752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>909496</t>
+          <t>995304</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>584480</t>
+          <t>959552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1079448</t>
+          <t>1033816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1308214</t>
+          <t>1198078</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1236940</t>
+          <t>1168841</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1456236</t>
+          <t>1225184</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2217710</t>
+          <t>2193382</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1663970</t>
+          <t>2149344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2427285</t>
+          <t>2238977</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -8281,17 +8281,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1683975</t>
+          <t>1564364</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1683975</t>
+          <t>1564364</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1683975</t>
+          <t>1564364</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1780876</t>
+          <t>1719732</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1780876</t>
+          <t>1719732</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1780876</t>
+          <t>1719732</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3464851</t>
+          <t>3284096</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3464851</t>
+          <t>3284096</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3464851</t>
+          <t>3284096</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
